--- a/data/indicadores/15_05_02_02_pbd.xlsx
+++ b/data/indicadores/15_05_02_02_pbd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDSN\Atlas2025\R_codes\Prueba_4\Input_indicadores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDSN\Atlas2025\R_codes\Final\Input_indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6527324-E966-4429-A58B-0B5B20585293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCB58E3-4DAE-46B0-AD4D-EB43F45A6286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{7B68B962-72E4-4C67-AAB7-2D1BEEF765C6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{7B68B962-72E4-4C67-AAB7-2D1BEEF765C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos originales (opcional)" sheetId="1" r:id="rId1"/>
@@ -28,17 +28,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1601,7 +1590,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1643,6 +1632,13 @@
       <b/>
       <sz val="9"/>
       <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1702,7 +1698,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1725,11 +1721,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1775,11 +1784,217 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2523,6 +2738,19 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77419393-69C7-4B9E-8F2B-BC7825333C3C}" name="Tabla2" displayName="Tabla2" ref="A1:D344" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
+  <autoFilter ref="A1:D344" xr:uid="{77419393-69C7-4B9E-8F2B-BC7825333C3C}"/>
+  <tableColumns count="4">
+    <tableColumn id="5" xr3:uid="{89BA80E3-22F0-4A89-B7AB-03F615CBABA8}" name="id" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{B7DDFC4F-4C9C-4E45-B46E-5A0807651089}" name="Municipio" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{F4E71F5F-24D1-476D-BAFC-C1904C123DB8}" name="Indicador 2012" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{44678FD0-5382-48EF-9532-53CDA1ECBC05}" name="Indicador 2024" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -20765,754 +20993,754 @@
     <col min="3" max="4" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>485</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="27" t="s">
         <v>512</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="27" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>10101</v>
+        <v>90503</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>482</v>
       </c>
       <c r="C2" s="6">
-        <v>0</v>
+        <v>1.3689271521057027E-2</v>
       </c>
       <c r="D2" s="6">
-        <v>7.8452828111055511E-3</v>
+        <v>1.3734351413043853E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>10102</v>
+        <v>11002</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C3" s="6">
-        <v>0</v>
+        <v>3.1519295226187953E-2</v>
       </c>
       <c r="D3" s="6">
-        <v>0</v>
+        <v>0.15987730149709606</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>10103</v>
+        <v>90402</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C4" s="6">
-        <v>0</v>
+        <v>2.612832326779501E-2</v>
       </c>
       <c r="D4" s="6">
-        <v>0</v>
+        <v>3.162543131870111E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>10201</v>
+        <v>20101</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C5" s="6">
-        <v>1.9724491559656148E-2</v>
+        <v>2.1683699808528599E-2</v>
       </c>
       <c r="D5" s="6">
-        <v>0.23049370636790434</v>
+        <v>0.11766259165135766</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>10202</v>
+        <v>11003</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C6" s="6">
-        <v>1.4703612636239561E-2</v>
+        <v>0.13038808312748493</v>
       </c>
       <c r="D6" s="6">
-        <v>3.6440426814160015E-2</v>
+        <v>0.50109780542339077</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>10301</v>
+        <v>70707</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="C7" s="6">
-        <v>0</v>
+        <v>9.6800082597472848E-3</v>
       </c>
       <c r="D7" s="6">
-        <v>0</v>
+        <v>0.31708187570681451</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>10302</v>
+        <v>60601</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>215</v>
       </c>
       <c r="C8" s="6">
-        <v>0</v>
+        <v>5.5281311465164663E-2</v>
       </c>
       <c r="D8" s="6">
-        <v>5.4412829657505598E-3</v>
+        <v>0.36968119656543796</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>10303</v>
+        <v>70503</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>390</v>
       </c>
       <c r="C9" s="6">
-        <v>0</v>
+        <v>9.4160047270034367E-2</v>
       </c>
       <c r="D9" s="6">
-        <v>4.3070855655778992E-2</v>
+        <v>2.025120003427789</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>10304</v>
+        <v>71201</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="C10" s="6">
-        <v>0</v>
+        <v>2.6935793844800854E-2</v>
       </c>
       <c r="D10" s="6">
-        <v>0</v>
+        <v>0.21782823130578241</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>10401</v>
+        <v>90401</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>394</v>
       </c>
       <c r="C11" s="6">
-        <v>0.19479729905615795</v>
+        <v>0.10187843767805958</v>
       </c>
       <c r="D11" s="6">
-        <v>0.23206315750459663</v>
+        <v>8.974889414762971E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>10402</v>
+        <v>90501</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>22</v>
+        <v>479</v>
       </c>
       <c r="C12" s="6">
-        <v>0</v>
+        <v>4.0971303293324469E-2</v>
       </c>
       <c r="D12" s="6">
-        <v>0</v>
+        <v>2.3233547266592155E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>10403</v>
+        <v>30303</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="C13" s="6">
-        <v>1.6537723437808391E-2</v>
+        <v>2.1553934611076259E-2</v>
       </c>
       <c r="D13" s="6">
-        <v>9.7079219527689053E-2</v>
+        <v>0.24145052422082577</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>10404</v>
+        <v>21401</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="C14" s="6">
-        <v>0</v>
+        <v>5.395433018272202E-2</v>
       </c>
       <c r="D14" s="6">
-        <v>0</v>
+        <v>0.15792774525487344</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>10405</v>
+        <v>90502</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>480</v>
       </c>
       <c r="C15" s="6">
-        <v>4.0182564096648887E-2</v>
+        <v>3.276832061013981E-2</v>
       </c>
       <c r="D15" s="6">
-        <v>0.15828032222456018</v>
+        <v>1.901734560941222E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>10501</v>
+        <v>90303</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>476</v>
       </c>
       <c r="C16" s="6">
-        <v>0.26667014194493788</v>
+        <v>2.8246508442810993E-2</v>
       </c>
       <c r="D16" s="6">
-        <v>0.76170425796877783</v>
+        <v>7.0352311661754735E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>10502</v>
+        <v>21402</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="C17" s="6">
-        <v>0.12179878095977237</v>
+        <v>0.12783706325980576</v>
       </c>
       <c r="D17" s="6">
-        <v>0.96496854963153256</v>
+        <v>0.16428134093471231</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>10601</v>
+        <v>90203</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>473</v>
       </c>
       <c r="C18" s="6">
-        <v>0</v>
+        <v>0.10232434515391299</v>
       </c>
       <c r="D18" s="6">
-        <v>0</v>
+        <v>0.21185884142306322</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>10602</v>
+        <v>10502</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="6">
-        <v>0</v>
+        <v>0.12179878095977237</v>
       </c>
       <c r="D19" s="6">
-        <v>0</v>
+        <v>0.96496854963153256</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>10701</v>
+        <v>21006</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="C20" s="6">
-        <v>0</v>
+        <v>9.4252883726922032E-2</v>
       </c>
       <c r="D20" s="6">
-        <v>3.7624765677173443E-3</v>
+        <v>0.77625418583221828</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>10702</v>
+        <v>20602</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="C21" s="6">
-        <v>2.0662212661597987E-2</v>
+        <v>7.9021065261737258E-2</v>
       </c>
       <c r="D21" s="6">
-        <v>2.5105398480569585E-2</v>
+        <v>0.41298978000005976</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>10703</v>
+        <v>60201</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>350</v>
       </c>
       <c r="C22" s="6">
-        <v>3.5601174618167961E-2</v>
+        <v>7.819745795317104E-2</v>
       </c>
       <c r="D22" s="6">
-        <v>0.51389688159019431</v>
+        <v>0.23473528694888682</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>10704</v>
+        <v>21001</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="C23" s="6">
-        <v>0</v>
+        <v>2.4952096318953978E-2</v>
       </c>
       <c r="D23" s="6">
-        <v>4.3592966867757037E-2</v>
+        <v>0.80549564450039646</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>10801</v>
+        <v>10201</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C24" s="6">
-        <v>5.9650784786605453E-2</v>
+        <v>1.9724491559656148E-2</v>
       </c>
       <c r="D24" s="6">
-        <v>0.26834664352797893</v>
+        <v>0.23049370636790434</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>10901</v>
+        <v>70702</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>43</v>
+        <v>398</v>
       </c>
       <c r="C25" s="6">
-        <v>0</v>
+        <v>0.31816361001233129</v>
       </c>
       <c r="D25" s="6">
-        <v>5.6136235858924056E-2</v>
+        <v>0.48739222076188882</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>10902</v>
+        <v>21501</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>44</v>
+        <v>149</v>
       </c>
       <c r="C26" s="6">
-        <v>0.11658170722749829</v>
+        <v>2.2556626959206016E-2</v>
       </c>
       <c r="D26" s="6">
-        <v>0.30145265123628573</v>
+        <v>5.2057602131000996E-2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>10903</v>
+        <v>71402</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>433</v>
       </c>
       <c r="C27" s="6">
-        <v>0</v>
+        <v>0.12701998898704076</v>
       </c>
       <c r="D27" s="6">
-        <v>4.1956611043824914E-2</v>
+        <v>0.15480613333219917</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>11001</v>
+        <v>10902</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C28" s="6">
-        <v>0.1650768048088318</v>
+        <v>0.11658170722749829</v>
       </c>
       <c r="D28" s="6">
-        <v>0.21933961051032219</v>
+        <v>0.30145265123628573</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>11002</v>
+        <v>70901</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="6">
-        <v>3.1519295226187953E-2</v>
-      </c>
-      <c r="D29" s="6">
-        <v>0.15987730149709606</v>
+        <v>411</v>
+      </c>
+      <c r="C29" s="7">
+        <v>8.3649446803819472E-2</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0.17464207469019427</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>11003</v>
+        <v>21105</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="C30" s="6">
-        <v>0.13038808312748493</v>
+        <v>0.11305114902301523</v>
       </c>
       <c r="D30" s="6">
-        <v>0.50109780542339077</v>
+        <v>0.92520243413927983</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>20101</v>
+        <v>70303</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>54</v>
+        <v>380</v>
       </c>
       <c r="C31" s="6">
-        <v>2.1683699808528599E-2</v>
+        <v>0.12404898830205037</v>
       </c>
       <c r="D31" s="6">
-        <v>0.11766259165135766</v>
+        <v>1.1566637893313838</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>20102</v>
+        <v>31202</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="C32" s="6">
-        <v>0</v>
+        <v>4.3465288458243108E-2</v>
       </c>
       <c r="D32" s="6">
-        <v>0.27024208276048661</v>
+        <v>4.8460677404079423E-2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>20103</v>
+        <v>11001</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C33" s="6">
-        <v>0</v>
+        <v>0.1650768048088318</v>
       </c>
       <c r="D33" s="6">
-        <v>1.0432468340394402E-2</v>
+        <v>0.21933961051032219</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>20104</v>
+        <v>20701</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="C34" s="6">
-        <v>0</v>
+        <v>1.9631196595943198E-2</v>
       </c>
       <c r="D34" s="6">
-        <v>0</v>
+        <v>0.28107352990037887</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>20105</v>
+        <v>20603</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C35" s="6">
-        <v>0</v>
+        <v>6.6458504158267373E-2</v>
       </c>
       <c r="D35" s="6">
-        <v>0</v>
+        <v>0.53526368703467286</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>20201</v>
+        <v>71502</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>60</v>
+        <v>437</v>
       </c>
       <c r="C36" s="6">
-        <v>0</v>
+        <v>9.5732985532659236E-3</v>
       </c>
       <c r="D36" s="6">
-        <v>0</v>
+        <v>0.18603598193553481</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>20202</v>
+        <v>10702</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C37" s="6">
-        <v>0</v>
+        <v>2.0662212661597987E-2</v>
       </c>
       <c r="D37" s="6">
-        <v>0</v>
+        <v>2.5105398480569585E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>20203</v>
+        <v>20502</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="7">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7">
-        <v>0</v>
+        <v>86</v>
+      </c>
+      <c r="C38" s="6">
+        <v>2.7597633857939494E-2</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.10132982166288916</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>20204</v>
+        <v>10703</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C39" s="6">
-        <v>0</v>
+        <v>3.5601174618167961E-2</v>
       </c>
       <c r="D39" s="6">
-        <v>0</v>
+        <v>0.51389688159019431</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>20205</v>
+        <v>71101</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>65</v>
+        <v>358</v>
       </c>
       <c r="C40" s="6">
-        <v>0</v>
+        <v>0.15821153184389056</v>
       </c>
       <c r="D40" s="6">
-        <v>0</v>
+        <v>0.8371662270510456</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>20206</v>
+        <v>21102</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="7">
-        <v>0</v>
-      </c>
-      <c r="D41" s="7">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1.8438966965001982E-2</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1.2637928284558806</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>20301</v>
+        <v>21103</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="C42" s="6">
         <v>0</v>
       </c>
       <c r="D42" s="6">
-        <v>0</v>
+        <v>3.9601806062432271E-2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>20302</v>
+        <v>70704</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="C43" s="6">
-        <v>0</v>
+        <v>0.11072481689409375</v>
       </c>
       <c r="D43" s="6">
-        <v>0</v>
+        <v>1.0557410071933421E-2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>20303</v>
+        <v>21601</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="C44" s="6">
-        <v>0</v>
+        <v>2.3899213968852237E-2</v>
       </c>
       <c r="D44" s="6">
-        <v>0</v>
+        <v>0.27362337969184103</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>20304</v>
+        <v>10401</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="C45" s="6">
-        <v>0</v>
+        <v>0.19479729905615795</v>
       </c>
       <c r="D45" s="6">
-        <v>0</v>
+        <v>0.23206315750459663</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>20305</v>
+        <v>60303</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>73</v>
+        <v>355</v>
       </c>
       <c r="C46" s="6">
-        <v>0</v>
+        <v>0.19150728254455138</v>
       </c>
       <c r="D46" s="6">
-        <v>0</v>
+        <v>0.44244189695765168</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>20306</v>
+        <v>90104</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>74</v>
+        <v>470</v>
       </c>
       <c r="C47" s="6">
-        <v>0</v>
+        <v>0.26824887653210744</v>
       </c>
       <c r="D47" s="6">
-        <v>0</v>
+        <v>0.43730645606278179</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>20307</v>
+        <v>60101</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="C48" s="6">
-        <v>0</v>
+        <v>1.0801450915877937E-2</v>
       </c>
       <c r="D48" s="6">
-        <v>0</v>
+        <v>0.29981005609977096</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>20308</v>
+        <v>20607</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C49" s="6">
-        <v>0</v>
+        <v>0.17046200378405568</v>
       </c>
       <c r="D49" s="6">
-        <v>0</v>
+        <v>0.66395668374458394</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>20401</v>
+        <v>22001</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="C50" s="6">
-        <v>0</v>
+        <v>0.2202429180226454</v>
       </c>
       <c r="D50" s="6">
-        <v>0</v>
+        <v>0.31429493301120814</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>20402</v>
+        <v>70804</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>79</v>
+        <v>408</v>
       </c>
       <c r="C51" s="6">
-        <v>1.5376473338976146E-2</v>
+        <v>0.20903350570629595</v>
       </c>
       <c r="D51" s="6">
-        <v>4.3936349043534967E-2</v>
+        <v>0.56894051027375003</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>20403</v>
+        <v>31601</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>80</v>
+        <v>230</v>
       </c>
       <c r="C52" s="6">
-        <v>0</v>
+        <v>8.0792269867408992E-3</v>
       </c>
       <c r="D52" s="6">
-        <v>0</v>
+        <v>7.6938650777562928E-2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>20404</v>
+        <v>10303</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="C53" s="6">
         <v>0</v>
       </c>
       <c r="D53" s="6">
-        <v>0</v>
+        <v>4.3070855655778992E-2</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>20405</v>
+        <v>10404</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="C54" s="6">
         <v>0</v>
@@ -21523,279 +21751,279 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>20501</v>
+        <v>21101</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="C55" s="6">
-        <v>0</v>
+        <v>6.4380688496774044E-2</v>
       </c>
       <c r="D55" s="6">
-        <v>6.2838247555263502E-2</v>
+        <v>0.62242159810654463</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>20502</v>
+        <v>31304</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C56" s="6">
-        <v>2.7597633857939494E-2</v>
-      </c>
-      <c r="D56" s="6">
-        <v>0.10132982166288916</v>
+        <v>219</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0</v>
+      </c>
+      <c r="D56" s="7">
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>20503</v>
+        <v>71403</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>87</v>
+        <v>434</v>
       </c>
       <c r="C57" s="6">
-        <v>0</v>
+        <v>0.34432036005587402</v>
       </c>
       <c r="D57" s="6">
-        <v>0.10453076149346063</v>
+        <v>1.1166037097216142</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>20601</v>
+        <v>21003</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C58" s="6">
-        <v>3.4012877581357563E-2</v>
+        <v>9.0832823426271483E-2</v>
       </c>
       <c r="D58" s="6">
-        <v>0.12053606620267038</v>
+        <v>1.1525363146035095</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>20602</v>
+        <v>90103</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>90</v>
+        <v>469</v>
       </c>
       <c r="C59" s="6">
-        <v>7.9021065261737258E-2</v>
+        <v>0.32970506406161704</v>
       </c>
       <c r="D59" s="6">
-        <v>0.41298978000005976</v>
+        <v>0.47877964825727243</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
-        <v>20603</v>
+        <v>90201</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>91</v>
+        <v>472</v>
       </c>
       <c r="C60" s="6">
-        <v>6.6458504158267373E-2</v>
+        <v>0.102116295556402</v>
       </c>
       <c r="D60" s="6">
-        <v>0.53526368703467286</v>
+        <v>6.6665266524600919E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>20604</v>
+        <v>20601</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C61" s="6">
-        <v>7.4599653521093989E-2</v>
+        <v>3.4012877581357563E-2</v>
       </c>
       <c r="D61" s="6">
-        <v>7.2600795965985454E-2</v>
+        <v>0.12053606620267038</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>20605</v>
+        <v>71401</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>93</v>
+        <v>432</v>
       </c>
       <c r="C62" s="6">
-        <v>0</v>
+        <v>0.13571728172619379</v>
       </c>
       <c r="D62" s="6">
-        <v>0</v>
+        <v>0.22705037749274634</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3">
-        <v>20606</v>
+        <v>71302</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>94</v>
+        <v>430</v>
       </c>
       <c r="C63" s="6">
-        <v>0.10674090095933143</v>
+        <v>2.752828165370827E-2</v>
       </c>
       <c r="D63" s="6">
-        <v>0.47427410898768801</v>
+        <v>0.15775590100214765</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3">
-        <v>20607</v>
+        <v>60501</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>95</v>
+        <v>361</v>
       </c>
       <c r="C64" s="6">
-        <v>0.17046200378405568</v>
+        <v>7.3392323984933722E-3</v>
       </c>
       <c r="D64" s="6">
-        <v>0.66395668374458394</v>
+        <v>0.20089606211517666</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3">
-        <v>20608</v>
+        <v>10405</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="C65" s="6">
-        <v>0.36882097159719573</v>
+        <v>4.0182564096648887E-2</v>
       </c>
       <c r="D65" s="6">
-        <v>0.7411263994972267</v>
+        <v>0.15828032222456018</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3">
-        <v>20701</v>
+        <v>10704</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="C66" s="6">
-        <v>1.9631196595943198E-2</v>
+        <v>0</v>
       </c>
       <c r="D66" s="6">
-        <v>0.28107352990037887</v>
+        <v>4.3592966867757037E-2</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3">
-        <v>20702</v>
+        <v>10202</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C67" s="6">
-        <v>1.0155944543295284E-2</v>
+        <v>1.4703612636239561E-2</v>
       </c>
       <c r="D67" s="6">
-        <v>9.6314991364647551E-2</v>
+        <v>3.6440426814160015E-2</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3">
-        <v>20801</v>
+        <v>70801</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>101</v>
+        <v>404</v>
       </c>
       <c r="C68" s="6">
-        <v>0</v>
+        <v>0.1793323671593389</v>
       </c>
       <c r="D68" s="6">
-        <v>0</v>
+        <v>0.40047724652567285</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3">
-        <v>20802</v>
+        <v>80802</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>102</v>
+        <v>462</v>
       </c>
       <c r="C69" s="6">
-        <v>0</v>
+        <v>1.7787426793790348E-2</v>
       </c>
       <c r="D69" s="6">
-        <v>0</v>
+        <v>9.0209310848399893E-2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3">
-        <v>20803</v>
+        <v>10302</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="C70" s="6">
         <v>0</v>
       </c>
       <c r="D70" s="6">
-        <v>0</v>
+        <v>5.4412829657505598E-3</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3">
-        <v>20804</v>
+        <v>71301</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>105</v>
+        <v>429</v>
       </c>
       <c r="C71" s="6">
-        <v>0</v>
+        <v>0.10600783251507911</v>
       </c>
       <c r="D71" s="6">
-        <v>0</v>
+        <v>0.11562560573732132</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3">
-        <v>20805</v>
+        <v>31201</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="C72" s="6">
-        <v>0</v>
+        <v>6.6416220034075643E-2</v>
       </c>
       <c r="D72" s="6">
-        <v>0</v>
+        <v>7.7695059772692351E-2</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3">
-        <v>20806</v>
+        <v>30203</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="C73" s="6">
         <v>0</v>
       </c>
       <c r="D73" s="6">
-        <v>0</v>
+        <v>3.7756255486715636E-2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3">
-        <v>20807</v>
+        <v>50502</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>110</v>
+        <v>307</v>
       </c>
       <c r="C74" s="6">
-        <v>0</v>
+        <v>5.7476052483600073E-3</v>
       </c>
       <c r="D74" s="6">
         <v>0</v>
@@ -21803,41 +22031,41 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3">
-        <v>20901</v>
+        <v>70302</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>112</v>
+        <v>378</v>
       </c>
       <c r="C75" s="6">
-        <v>0</v>
+        <v>0.15818733731332379</v>
       </c>
       <c r="D75" s="6">
-        <v>2.2040040758953029E-2</v>
+        <v>1.4907538333700081</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3">
-        <v>20902</v>
+        <v>10403</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="C76" s="6">
-        <v>1.0191575586980183E-2</v>
+        <v>1.6537723437808391E-2</v>
       </c>
       <c r="D76" s="6">
-        <v>8.0241985400303882E-3</v>
+        <v>9.7079219527689053E-2</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3">
-        <v>20903</v>
+        <v>30201</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="C77" s="6">
-        <v>0</v>
+        <v>3.5962155870477041E-3</v>
       </c>
       <c r="D77" s="6">
         <v>0</v>
@@ -21845,220 +22073,220 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3">
-        <v>20904</v>
+        <v>70903</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>115</v>
+        <v>413</v>
       </c>
       <c r="C78" s="6">
-        <v>0</v>
+        <v>0.26272761589224441</v>
       </c>
       <c r="D78" s="6">
-        <v>0</v>
+        <v>0.47805610949675609</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3">
-        <v>20905</v>
+        <v>20606</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C79" s="6">
-        <v>0</v>
+        <v>0.10674090095933143</v>
       </c>
       <c r="D79" s="6">
-        <v>9.0593040469730657E-2</v>
+        <v>0.47427410898768801</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3">
-        <v>21001</v>
+        <v>10103</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="C80" s="6">
-        <v>2.4952096318953978E-2</v>
+        <v>0</v>
       </c>
       <c r="D80" s="6">
-        <v>0.80549564450039646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="3">
-        <v>21002</v>
+        <v>10501</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>1.2014918897546889E-2</v>
+        <v>0.26667014194493788</v>
       </c>
       <c r="D81" s="6">
-        <v>0.22258050958961234</v>
+        <v>0.76170425796877783</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3">
-        <v>21003</v>
+        <v>60302</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>119</v>
+        <v>354</v>
       </c>
       <c r="C82" s="6">
-        <v>9.0832823426271483E-2</v>
+        <v>0.2704646046512198</v>
       </c>
       <c r="D82" s="6">
-        <v>1.1525363146035095</v>
+        <v>0.48739707025536005</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="3">
-        <v>21004</v>
+        <v>80303</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>120</v>
+        <v>394</v>
       </c>
       <c r="C83" s="6">
-        <v>0</v>
+        <v>1.4570782745680983E-2</v>
       </c>
       <c r="D83" s="6">
-        <v>0</v>
+        <v>8.2752073179950439E-2</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="3">
-        <v>21005</v>
+        <v>80201</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>121</v>
+        <v>442</v>
       </c>
       <c r="C84" s="6">
-        <v>0</v>
+        <v>0.27405699353249757</v>
       </c>
       <c r="D84" s="6">
-        <v>9.3156828905498673E-2</v>
+        <v>0.10031484288148462</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="3">
-        <v>21006</v>
+        <v>10402</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="C85" s="6">
-        <v>9.4252883726922032E-2</v>
+        <v>0</v>
       </c>
       <c r="D85" s="6">
-        <v>0.77625418583221828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="3">
-        <v>21101</v>
+        <v>21002</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C86" s="6">
-        <v>6.4380688496774044E-2</v>
+        <v>1.2014918897546889E-2</v>
       </c>
       <c r="D86" s="6">
-        <v>0.62242159810654463</v>
+        <v>0.22258050958961234</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="3">
-        <v>21102</v>
+        <v>70301</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>126</v>
+        <v>376</v>
       </c>
       <c r="C87" s="6">
-        <v>1.8438966965001982E-2</v>
+        <v>0.22171309238431139</v>
       </c>
       <c r="D87" s="6">
-        <v>1.2637928284558806</v>
+        <v>0.71810049543625021</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="3">
-        <v>21103</v>
+        <v>70501</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>128</v>
+        <v>387</v>
       </c>
       <c r="C88" s="6">
-        <v>0</v>
+        <v>0.2329082844718246</v>
       </c>
       <c r="D88" s="6">
-        <v>3.9601806062432271E-2</v>
+        <v>1.4269415322509753</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="3">
-        <v>21104</v>
+        <v>90302</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>129</v>
+        <v>361</v>
       </c>
       <c r="C89" s="6">
-        <v>0.31685384877930767</v>
+        <v>8.1918509521273802E-2</v>
       </c>
       <c r="D89" s="6">
-        <v>0.89481345431466197</v>
+        <v>0.10120030302316683</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="3">
-        <v>21105</v>
+        <v>10101</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
       <c r="C90" s="6">
-        <v>0.11305114902301523</v>
+        <v>0</v>
       </c>
       <c r="D90" s="6">
-        <v>0.92520243413927983</v>
+        <v>7.8452828111055511E-3</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="3">
-        <v>21201</v>
+        <v>31301</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="C91" s="6">
         <v>0</v>
       </c>
       <c r="D91" s="6">
-        <v>0</v>
+        <v>5.0763320402809177E-3</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="3">
-        <v>21202</v>
+        <v>80801</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>133</v>
+        <v>461</v>
       </c>
       <c r="C92" s="6">
-        <v>0</v>
+        <v>1.5310409880997369E-2</v>
       </c>
       <c r="D92" s="6">
-        <v>0</v>
+        <v>4.0663623654086378E-2</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="3">
-        <v>21203</v>
+        <v>10301</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="C93" s="6">
         <v>0</v>
@@ -22069,80 +22297,80 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="3">
-        <v>21204</v>
+        <v>70802</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>135</v>
+        <v>405</v>
       </c>
       <c r="C94" s="6">
-        <v>0</v>
+        <v>0.15941492169850319</v>
       </c>
       <c r="D94" s="6">
-        <v>0</v>
+        <v>0.11726882968894096</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="3">
-        <v>21301</v>
+        <v>20501</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="C95" s="6">
         <v>0</v>
       </c>
       <c r="D95" s="6">
-        <v>0</v>
+        <v>6.2838247555263502E-2</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="3">
-        <v>21302</v>
+        <v>21104</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C96" s="6">
-        <v>0</v>
+        <v>0.31685384877930767</v>
       </c>
       <c r="D96" s="6">
-        <v>0</v>
+        <v>0.89481345431466197</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3">
-        <v>21303</v>
+        <v>10801</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>140</v>
+        <v>41</v>
       </c>
       <c r="C97" s="6">
-        <v>0</v>
+        <v>5.9650784786605453E-2</v>
       </c>
       <c r="D97" s="6">
-        <v>0</v>
+        <v>0.26834664352797893</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3">
-        <v>21304</v>
+        <v>70904</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>141</v>
+        <v>414</v>
       </c>
       <c r="C98" s="6">
-        <v>0</v>
+        <v>0.27802484702985353</v>
       </c>
       <c r="D98" s="6">
-        <v>0</v>
+        <v>0.25291672115702429</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3">
-        <v>21305</v>
+        <v>30902</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="C99" s="6">
         <v>0</v>
@@ -22153,136 +22381,136 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3">
-        <v>21306</v>
+        <v>90202</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>143</v>
+        <v>306</v>
       </c>
       <c r="C100" s="6">
-        <v>0</v>
+        <v>0.14001641673480761</v>
       </c>
       <c r="D100" s="6">
-        <v>0</v>
+        <v>7.7111164966284229E-2</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3">
-        <v>21307</v>
+        <v>30202</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="C101" s="6">
         <v>0</v>
       </c>
       <c r="D101" s="6">
-        <v>0</v>
+        <v>5.9069059423448513E-2</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3">
-        <v>21401</v>
+        <v>70805</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>146</v>
+        <v>409</v>
       </c>
       <c r="C102" s="6">
-        <v>5.395433018272202E-2</v>
+        <v>0.11420307303802221</v>
       </c>
       <c r="D102" s="6">
-        <v>0.15792774525487344</v>
+        <v>0.3128911844334506</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3">
-        <v>21402</v>
+        <v>80901</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C103" s="6">
-        <v>0.12783706325980576</v>
-      </c>
-      <c r="D103" s="6">
-        <v>0.16428134093471231</v>
+        <v>464</v>
+      </c>
+      <c r="C103" s="9">
+        <v>1.6869993655159673E-2</v>
+      </c>
+      <c r="D103" s="9">
+        <v>8.655804011357153E-2</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3">
-        <v>21501</v>
+        <v>30301</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C104" s="6">
-        <v>2.2556626959206016E-2</v>
+        <v>0</v>
       </c>
       <c r="D104" s="6">
-        <v>5.2057602131000996E-2</v>
+        <v>0.10802747886397158</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3">
-        <v>21502</v>
+        <v>20702</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="C105" s="6">
-        <v>0.15448030757315728</v>
+        <v>1.0155944543295284E-2</v>
       </c>
       <c r="D105" s="6">
-        <v>0.32864151547079928</v>
+        <v>9.6314991364647551E-2</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3">
-        <v>21601</v>
+        <v>70902</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="C106" s="6">
-        <v>2.3899213968852237E-2</v>
+        <v>0.38165661813859109</v>
       </c>
       <c r="D106" s="6">
-        <v>0.27362337969184103</v>
+        <v>0.53153545596391372</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3">
-        <v>21602</v>
+        <v>50402</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>154</v>
+        <v>301</v>
       </c>
       <c r="C107" s="6">
         <v>0</v>
       </c>
       <c r="D107" s="6">
-        <v>0.10112228123254695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3">
-        <v>21701</v>
+        <v>20608</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="C108" s="6">
-        <v>0</v>
+        <v>0.36882097159719573</v>
       </c>
       <c r="D108" s="6">
-        <v>0</v>
+        <v>0.7411263994972267</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3">
-        <v>21702</v>
+        <v>10601</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c r="C109" s="6">
         <v>0</v>
@@ -22293,10 +22521,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3">
-        <v>21703</v>
+        <v>31203</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="C110" s="6">
         <v>0</v>
@@ -22307,24 +22535,24 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3">
-        <v>21801</v>
+        <v>70706</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>160</v>
+        <v>402</v>
       </c>
       <c r="C111" s="6">
-        <v>0</v>
+        <v>0.4150614455170637</v>
       </c>
       <c r="D111" s="6">
-        <v>0</v>
+        <v>0.38013493459319331</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3">
-        <v>21802</v>
+        <v>10304</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="C112" s="6">
         <v>0</v>
@@ -22335,83 +22563,83 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3">
-        <v>21803</v>
+        <v>30302</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C113" s="6">
         <v>0</v>
       </c>
       <c r="D113" s="6">
-        <v>0</v>
+        <v>0.16459137815832131</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3">
-        <v>21901</v>
+        <v>70701</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>165</v>
+        <v>397</v>
       </c>
       <c r="C114" s="6">
-        <v>0</v>
+        <v>0.69799514739688251</v>
       </c>
       <c r="D114" s="6">
-        <v>0</v>
+        <v>0.18618281156905758</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="3">
-        <v>21902</v>
+        <v>80501</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>166</v>
+        <v>377</v>
       </c>
       <c r="C115" s="6">
-        <v>0</v>
+        <v>1.789118067534488E-2</v>
       </c>
       <c r="D115" s="6">
-        <v>0</v>
+        <v>6.0933048198979232E-2</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="3">
-        <v>22001</v>
+        <v>80402</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>167</v>
+        <v>452</v>
       </c>
       <c r="C116" s="6">
-        <v>0.2202429180226454</v>
+        <v>1.1086441351722799E-2</v>
       </c>
       <c r="D116" s="6">
-        <v>0.31429493301120814</v>
+        <v>2.866831763855035E-2</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3">
-        <v>22002</v>
+        <v>50301</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>168</v>
+        <v>296</v>
       </c>
       <c r="C117" s="6">
-        <v>0.66353817716694241</v>
+        <v>0</v>
       </c>
       <c r="D117" s="6">
-        <v>2.3444708149782567</v>
+        <v>3.2162160898791458E-3</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="3">
-        <v>30101</v>
+        <v>31302</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="C118" s="6">
-        <v>2.0436011538197414E-2</v>
+        <v>0</v>
       </c>
       <c r="D118" s="6">
         <v>0</v>
@@ -22419,13 +22647,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="3">
-        <v>30201</v>
+        <v>30101</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C119" s="6">
-        <v>3.5962155870477041E-3</v>
+        <v>2.0436011538197414E-2</v>
       </c>
       <c r="D119" s="6">
         <v>0</v>
@@ -22433,80 +22661,80 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3">
-        <v>30202</v>
+        <v>30904</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="C120" s="6">
         <v>0</v>
       </c>
       <c r="D120" s="6">
-        <v>5.9069059423448513E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="3">
-        <v>30203</v>
+        <v>71105</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>174</v>
+        <v>424</v>
       </c>
       <c r="C121" s="6">
-        <v>0</v>
+        <v>5.7659280123938887E-2</v>
       </c>
       <c r="D121" s="6">
-        <v>3.7756255486715636E-2</v>
+        <v>0.45725168761237522</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3">
-        <v>30301</v>
+        <v>50501</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>176</v>
+        <v>306</v>
       </c>
       <c r="C122" s="6">
         <v>0</v>
       </c>
       <c r="D122" s="6">
-        <v>0.10802747886397158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3">
-        <v>30302</v>
+        <v>21005</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="C123" s="6">
         <v>0</v>
       </c>
       <c r="D123" s="6">
-        <v>0.16459137815832131</v>
+        <v>9.3156828905498673E-2</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="3">
-        <v>30303</v>
+        <v>80302</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>179</v>
+        <v>446</v>
       </c>
       <c r="C124" s="6">
-        <v>2.1553934611076259E-2</v>
+        <v>0.27451855753058152</v>
       </c>
       <c r="D124" s="6">
-        <v>0.24145052422082577</v>
+        <v>0.31751526008971076</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="3">
-        <v>30401</v>
+        <v>10102</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>181</v>
+        <v>9</v>
       </c>
       <c r="C125" s="6">
         <v>0</v>
@@ -22517,52 +22745,52 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="3">
-        <v>30402</v>
+        <v>90102</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C126" s="6">
-        <v>0</v>
-      </c>
-      <c r="D126" s="6">
-        <v>0</v>
+        <v>468</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0.57291852844216251</v>
+      </c>
+      <c r="D126" s="7">
+        <v>0.70467817718445447</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="3">
-        <v>30403</v>
+        <v>70803</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>184</v>
+        <v>406</v>
       </c>
       <c r="C127" s="6">
-        <v>0</v>
+        <v>3.1912411417968516E-2</v>
       </c>
       <c r="D127" s="6">
-        <v>0</v>
+        <v>0.11776422078833867</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="3">
-        <v>30404</v>
+        <v>60401</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>185</v>
+        <v>357</v>
       </c>
       <c r="C128" s="6">
         <v>0</v>
       </c>
       <c r="D128" s="6">
-        <v>0</v>
+        <v>0.40945696635553408</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="3">
-        <v>30501</v>
+        <v>30702</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C129" s="6">
         <v>0</v>
@@ -22573,24 +22801,24 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="3">
-        <v>30502</v>
+        <v>60202</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>187</v>
+        <v>351</v>
       </c>
       <c r="C130" s="6">
-        <v>0</v>
+        <v>0.29316310885077762</v>
       </c>
       <c r="D130" s="6">
-        <v>0</v>
+        <v>0.97303880498730266</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="3">
-        <v>30601</v>
+        <v>50401</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>188</v>
+        <v>300</v>
       </c>
       <c r="C131" s="6">
         <v>0</v>
@@ -22601,10 +22829,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="3">
-        <v>30602</v>
+        <v>30901</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C132" s="6">
         <v>0</v>
@@ -22615,66 +22843,66 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="3">
-        <v>30701</v>
+        <v>22002</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="C133" s="6">
-        <v>0</v>
+        <v>0.66353817716694241</v>
       </c>
       <c r="D133" s="6">
-        <v>0</v>
+        <v>2.3444708149782567</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="3">
-        <v>30702</v>
+        <v>31002</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="C134" s="6">
-        <v>0</v>
+        <v>0.26436179155459671</v>
       </c>
       <c r="D134" s="6">
-        <v>0</v>
+        <v>0.2523912278836391</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3">
-        <v>30703</v>
+        <v>31003</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C135" s="6">
-        <v>0</v>
+        <v>0.27749415739992478</v>
       </c>
       <c r="D135" s="6">
-        <v>0</v>
+        <v>0.52151255609116354</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="3">
-        <v>30801</v>
+        <v>21602</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="C136" s="6">
         <v>0</v>
       </c>
       <c r="D136" s="6">
-        <v>0</v>
+        <v>0.10112228123254695</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="3">
-        <v>30802</v>
+        <v>30402</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C137" s="6">
         <v>0</v>
@@ -22685,83 +22913,83 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3">
-        <v>30803</v>
+        <v>70401</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>198</v>
+        <v>382</v>
       </c>
       <c r="C138" s="6">
-        <v>0</v>
+        <v>0.90973365701831221</v>
       </c>
       <c r="D138" s="6">
-        <v>0</v>
+        <v>0.40420673088101516</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="3">
-        <v>30901</v>
+        <v>80301</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>199</v>
+        <v>445</v>
       </c>
       <c r="C139" s="6">
-        <v>0</v>
+        <v>6.5460467625967411E-2</v>
       </c>
       <c r="D139" s="6">
-        <v>0</v>
+        <v>0.15209644523507648</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="3">
-        <v>30902</v>
+        <v>21502</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C140" s="6">
-        <v>0</v>
+        <v>0.15448030757315728</v>
       </c>
       <c r="D140" s="6">
-        <v>0</v>
+        <v>0.32864151547079928</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="3">
-        <v>30903</v>
+        <v>70705</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C141" s="6">
-        <v>0.15382442459868478</v>
+        <v>1.1233568250840498</v>
       </c>
       <c r="D141" s="6">
-        <v>0</v>
+        <v>0.37316210800105076</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="3">
-        <v>30904</v>
+        <v>20503</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>202</v>
+        <v>87</v>
       </c>
       <c r="C142" s="6">
         <v>0</v>
       </c>
       <c r="D142" s="6">
-        <v>0</v>
+        <v>0.10453076149346063</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="3">
-        <v>30905</v>
+        <v>30903</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C143" s="6">
-        <v>0</v>
+        <v>0.15382442459868478</v>
       </c>
       <c r="D143" s="6">
         <v>0</v>
@@ -22769,2817 +22997,2205 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="3">
-        <v>31001</v>
+        <v>20402</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="C144" s="6">
-        <v>0</v>
+        <v>1.5376473338976146E-2</v>
       </c>
       <c r="D144" s="6">
-        <v>7.948729892321385E-3</v>
+        <v>4.3936349043534967E-2</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="3">
-        <v>31002</v>
+        <v>90301</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>206</v>
+        <v>475</v>
       </c>
       <c r="C145" s="6">
-        <v>0.26436179155459671</v>
+        <v>0.20292288064260233</v>
       </c>
       <c r="D145" s="6">
-        <v>0.2523912278836391</v>
+        <v>0.30084816334701681</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="3">
-        <v>31003</v>
+        <v>31206</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C146" s="6">
-        <v>0.27749415739992478</v>
+        <v>0.94173762295871977</v>
       </c>
       <c r="D146" s="6">
-        <v>0.52151255609116354</v>
+        <v>0.97169971873777672</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="3">
-        <v>31101</v>
+        <v>80101</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>208</v>
+        <v>440</v>
       </c>
       <c r="C147" s="6">
-        <v>0</v>
+        <v>4.8410211703786739E-2</v>
       </c>
       <c r="D147" s="6">
-        <v>0</v>
+        <v>0.1136897208467646</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="3">
-        <v>31201</v>
+        <v>31602</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C148" s="6">
-        <v>6.6416220034075643E-2</v>
+        <v>0.61292790114114759</v>
       </c>
       <c r="D148" s="6">
-        <v>7.7695059772692351E-2</v>
+        <v>1.641721781178642</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3">
-        <v>31202</v>
+        <v>80102</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>211</v>
+        <v>421</v>
       </c>
       <c r="C149" s="6">
-        <v>4.3465288458243108E-2</v>
+        <v>8.63432040934385E-2</v>
       </c>
       <c r="D149" s="6">
-        <v>4.8460677404079423E-2</v>
+        <v>0.42676030714172852</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="3">
-        <v>31203</v>
+        <v>80602</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>212</v>
+        <v>456</v>
       </c>
       <c r="C150" s="6">
-        <v>0</v>
+        <v>0.24319717043159192</v>
       </c>
       <c r="D150" s="6">
-        <v>0</v>
+        <v>0.93997682372846725</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="3">
-        <v>31204</v>
+        <v>80202</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>213</v>
+        <v>443</v>
       </c>
       <c r="C151" s="6">
-        <v>0.24006397558580389</v>
+        <v>0.74901975644436691</v>
       </c>
       <c r="D151" s="6">
-        <v>0.68336113903388518</v>
+        <v>0.19793781949335393</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3">
-        <v>31205</v>
+        <v>31001</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C152" s="6">
-        <v>0.62433371235654644</v>
+        <v>0</v>
       </c>
       <c r="D152" s="6">
-        <v>1.2655690051550248</v>
+        <v>7.948729892321385E-3</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="3">
-        <v>31206</v>
+        <v>60301</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>215</v>
+        <v>353</v>
       </c>
       <c r="C153" s="6">
-        <v>0.94173762295871977</v>
+        <v>1.2901309453422689</v>
       </c>
       <c r="D153" s="6">
-        <v>0.97169971873777672</v>
+        <v>1.1802105164082988</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="3">
-        <v>31301</v>
+        <v>80701</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>216</v>
+        <v>458</v>
       </c>
       <c r="C154" s="6">
-        <v>0</v>
+        <v>3.5308274054465745E-2</v>
       </c>
       <c r="D154" s="6">
-        <v>5.0763320402809177E-3</v>
+        <v>4.2324546221992658E-2</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="3">
-        <v>31302</v>
+        <v>71501</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>217</v>
+        <v>436</v>
       </c>
       <c r="C155" s="6">
-        <v>0</v>
+        <v>0.67137201734431162</v>
       </c>
       <c r="D155" s="6">
-        <v>0</v>
+        <v>1.8503186071940834</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="3">
-        <v>31303</v>
+        <v>31204</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C156" s="6">
-        <v>0</v>
+        <v>0.24006397558580389</v>
       </c>
       <c r="D156" s="6">
-        <v>0</v>
+        <v>0.68336113903388518</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="3">
-        <v>31304</v>
+        <v>71102</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C157" s="7">
-        <v>0</v>
-      </c>
-      <c r="D157" s="7">
-        <v>0</v>
+        <v>421</v>
+      </c>
+      <c r="C157" s="6">
+        <v>0.98870419833237566</v>
+      </c>
+      <c r="D157" s="6">
+        <v>1.1873559747518225</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3">
-        <v>31401</v>
+        <v>20102</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>221</v>
+        <v>55</v>
       </c>
       <c r="C158" s="6">
         <v>0</v>
       </c>
       <c r="D158" s="6">
-        <v>0</v>
+        <v>0.27024208276048661</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="3">
-        <v>31402</v>
+        <v>71103</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>223</v>
+        <v>422</v>
       </c>
       <c r="C159" s="6">
-        <v>0</v>
+        <v>0.72011588778878011</v>
       </c>
       <c r="D159" s="6">
-        <v>0</v>
+        <v>1.1671566397954432</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="3">
-        <v>31403</v>
+        <v>80601</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>224</v>
+        <v>455</v>
       </c>
       <c r="C160" s="6">
-        <v>0</v>
+        <v>1.5874399110218092E-2</v>
       </c>
       <c r="D160" s="6">
-        <v>0</v>
+        <v>5.0164238174668578E-2</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="3">
-        <v>31404</v>
+        <v>20905</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>226</v>
+        <v>116</v>
       </c>
       <c r="C161" s="6">
         <v>0</v>
       </c>
       <c r="D161" s="6">
-        <v>0</v>
+        <v>9.0593040469730657E-2</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="3">
-        <v>31405</v>
+        <v>80304</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>227</v>
+        <v>447</v>
       </c>
       <c r="C162" s="6">
-        <v>0</v>
+        <v>0.3353843734033361</v>
       </c>
       <c r="D162" s="6">
-        <v>0</v>
+        <v>0.46887023447927562</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3">
-        <v>31501</v>
+        <v>80401</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>229</v>
+        <v>450</v>
       </c>
       <c r="C163" s="6">
-        <v>0</v>
+        <v>5.6304779707764846E-2</v>
       </c>
       <c r="D163" s="6">
-        <v>0</v>
+        <v>5.7388225745097617E-2</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="3">
-        <v>31601</v>
+        <v>31205</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C164" s="6">
-        <v>8.0792269867408992E-3</v>
+        <v>0.62433371235654644</v>
       </c>
       <c r="D164" s="6">
-        <v>7.6938650777562928E-2</v>
+        <v>1.2655690051550248</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3">
-        <v>31602</v>
+        <v>70703</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>231</v>
+        <v>399</v>
       </c>
       <c r="C165" s="6">
-        <v>0.61292790114114759</v>
+        <v>1.279794675919192</v>
       </c>
       <c r="D165" s="6">
-        <v>1.641721781178642</v>
+        <v>1.0232522378634807</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3">
-        <v>40101</v>
+        <v>70105</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="C166" s="6">
-        <v>0</v>
+        <v>1.5668017515077088</v>
       </c>
       <c r="D166" s="6">
-        <v>0</v>
+        <v>0.68246890169232532</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="3">
-        <v>40102</v>
+        <v>90101</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>233</v>
+        <v>467</v>
       </c>
       <c r="C167" s="6">
-        <v>0</v>
+        <v>0.83323099028835657</v>
       </c>
       <c r="D167" s="6">
-        <v>0</v>
+        <v>1.1045815777623671</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="3">
-        <v>40103</v>
+        <v>80702</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>234</v>
+        <v>422</v>
       </c>
       <c r="C168" s="6">
-        <v>0</v>
+        <v>2.3948495043991817E-2</v>
       </c>
       <c r="D168" s="6">
-        <v>0</v>
+        <v>3.2937244678818874E-2</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="3">
-        <v>40104</v>
+        <v>70403</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>235</v>
+        <v>384</v>
       </c>
       <c r="C169" s="6">
-        <v>0</v>
+        <v>0.99301048037412809</v>
       </c>
       <c r="D169" s="6">
-        <v>0</v>
+        <v>0.63892684706017577</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="3">
-        <v>40201</v>
+        <v>70603</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>238</v>
+        <v>395</v>
       </c>
       <c r="C170" s="6">
-        <v>0</v>
+        <v>0.96128956604420357</v>
       </c>
       <c r="D170" s="6">
-        <v>0</v>
+        <v>1.436853633353145</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="3">
-        <v>40202</v>
+        <v>80803</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>239</v>
+        <v>463</v>
       </c>
       <c r="C171" s="6">
-        <v>0</v>
+        <v>7.6598096465664385E-3</v>
       </c>
       <c r="D171" s="6">
-        <v>0</v>
+        <v>0.10281896284401074</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="3">
-        <v>40301</v>
+        <v>80703</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>241</v>
+        <v>459</v>
       </c>
       <c r="C172" s="6">
-        <v>0</v>
+        <v>3.3030824990643956E-2</v>
       </c>
       <c r="D172" s="6">
-        <v>0</v>
+        <v>0.15730275735975138</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="3">
-        <v>40302</v>
+        <v>70103</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>242</v>
+        <v>369</v>
       </c>
       <c r="C173" s="6">
-        <v>0</v>
+        <v>2.0781885264475592</v>
       </c>
       <c r="D173" s="6">
-        <v>0</v>
+        <v>0.82782879464268866</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="3">
-        <v>40401</v>
+        <v>70402</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>244</v>
+        <v>383</v>
       </c>
       <c r="C174" s="6">
-        <v>0</v>
+        <v>1.4887127163770957</v>
       </c>
       <c r="D174" s="6">
-        <v>0</v>
+        <v>0.79416795556073416</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="3">
-        <v>40402</v>
+        <v>70404</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>245</v>
+        <v>385</v>
       </c>
       <c r="C175" s="6">
-        <v>0</v>
+        <v>1.3000699794434905</v>
       </c>
       <c r="D175" s="6">
-        <v>0</v>
+        <v>1.5693251307299438</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="3">
-        <v>40501</v>
+        <v>71503</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>247</v>
+        <v>363</v>
       </c>
       <c r="C176" s="6">
-        <v>0</v>
+        <v>1.8933227627282803</v>
       </c>
       <c r="D176" s="6">
-        <v>0</v>
+        <v>1.991867949966813</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="3">
-        <v>40502</v>
+        <v>70502</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>248</v>
+        <v>389</v>
       </c>
       <c r="C177" s="6">
-        <v>0</v>
+        <v>1.8331428765239755</v>
       </c>
       <c r="D177" s="6">
-        <v>0</v>
+        <v>1.08032610676566</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="3">
-        <v>40503</v>
+        <v>70104</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>249</v>
+        <v>371</v>
       </c>
       <c r="C178" s="6">
-        <v>0</v>
+        <v>2.2164392705694982</v>
       </c>
       <c r="D178" s="6">
-        <v>0</v>
+        <v>0.87534761156129914</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="3">
-        <v>40504</v>
+        <v>70602</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>250</v>
+        <v>393</v>
       </c>
       <c r="C179" s="6">
-        <v>0</v>
+        <v>1.796691669738379</v>
       </c>
       <c r="D179" s="6">
-        <v>0</v>
+        <v>1.7082854665859581</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3">
-        <v>40505</v>
+        <v>70601</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>251</v>
+        <v>392</v>
       </c>
       <c r="C180" s="6">
-        <v>0</v>
+        <v>2.2664105284764116</v>
       </c>
       <c r="D180" s="6">
-        <v>0</v>
+        <v>0.87691862164175327</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="3">
-        <v>40601</v>
+        <v>71005</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>252</v>
+        <v>306</v>
       </c>
       <c r="C181" s="6">
-        <v>0</v>
+        <v>0.83732866444377829</v>
       </c>
       <c r="D181" s="6">
-        <v>0</v>
+        <v>0.40496914918942989</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="3">
-        <v>40602</v>
+        <v>71106</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>254</v>
+        <v>425</v>
       </c>
       <c r="C182" s="6">
-        <v>0</v>
+        <v>1.3901264518908389</v>
       </c>
       <c r="D182" s="6">
-        <v>0</v>
+        <v>0.6055652299402593</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="3">
-        <v>40603</v>
+        <v>70201</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>255</v>
+        <v>373</v>
       </c>
       <c r="C183" s="6">
-        <v>0</v>
+        <v>1.0364682810050185</v>
       </c>
       <c r="D183" s="6">
-        <v>0</v>
+        <v>0.5772936275058056</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="3">
-        <v>40701</v>
+        <v>71001</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>257</v>
+        <v>416</v>
       </c>
       <c r="C184" s="6">
-        <v>0</v>
+        <v>0.839299147827123</v>
       </c>
       <c r="D184" s="6">
-        <v>0</v>
+        <v>0.84922352489470776</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="3">
-        <v>40702</v>
+        <v>70102</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>259</v>
+        <v>368</v>
       </c>
       <c r="C185" s="6">
-        <v>0</v>
+        <v>1.1351462384259183</v>
       </c>
       <c r="D185" s="6">
-        <v>0</v>
+        <v>1.205676030834425</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3">
-        <v>40801</v>
+        <v>71002</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>261</v>
+        <v>417</v>
       </c>
       <c r="C186" s="6">
-        <v>0</v>
+        <v>1.0019892716499768</v>
       </c>
       <c r="D186" s="6">
-        <v>0</v>
+        <v>0.54465246490061781</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3">
-        <v>40802</v>
+        <v>71004</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>262</v>
+        <v>419</v>
       </c>
       <c r="C187" s="6">
-        <v>0</v>
+        <v>0.4805018937720989</v>
       </c>
       <c r="D187" s="6">
-        <v>0</v>
+        <v>0.21432220244416472</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="3">
-        <v>40901</v>
+        <v>70101</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>263</v>
+        <v>367</v>
       </c>
       <c r="C188" s="6">
-        <v>0</v>
+        <v>1.6599139792571078</v>
       </c>
       <c r="D188" s="6">
-        <v>0</v>
+        <v>0.82365093389118582</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3">
-        <v>40902</v>
+        <v>70202</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>264</v>
+        <v>374</v>
       </c>
       <c r="C189" s="6">
-        <v>0</v>
+        <v>0.6773711273295725</v>
       </c>
       <c r="D189" s="6">
-        <v>0</v>
+        <v>0.49182012540925574</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="3">
-        <v>40903</v>
+        <v>71003</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>265</v>
+        <v>418</v>
       </c>
       <c r="C190" s="6">
-        <v>0</v>
+        <v>1.0114631065388455</v>
       </c>
       <c r="D190" s="6">
-        <v>0</v>
+        <v>0.96431486429779012</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="3">
-        <v>41001</v>
+        <v>71104</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>267</v>
+        <v>423</v>
       </c>
       <c r="C191" s="6">
-        <v>0</v>
+        <v>4.3210677073578463</v>
       </c>
       <c r="D191" s="6">
-        <v>0</v>
+        <v>0.64172671834567141</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="3">
-        <v>41101</v>
+        <v>10602</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C192" s="6">
-        <v>0</v>
-      </c>
-      <c r="D192" s="6">
-        <v>0</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C192" s="6"/>
+      <c r="D192" s="6"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="3">
-        <v>41201</v>
+        <v>10701</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C193" s="6">
-        <v>0</v>
-      </c>
-      <c r="D193" s="6">
-        <v>0</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="C193" s="6"/>
+      <c r="D193" s="6"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="3">
-        <v>41202</v>
+        <v>10901</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C194" s="6">
-        <v>0</v>
-      </c>
-      <c r="D194" s="6">
-        <v>0</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C194" s="6"/>
+      <c r="D194" s="6"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="3">
-        <v>41301</v>
+        <v>10903</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C195" s="6">
-        <v>0</v>
-      </c>
-      <c r="D195" s="6">
-        <v>0</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C195" s="6"/>
+      <c r="D195" s="6"/>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="3">
-        <v>41401</v>
+        <v>20103</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C196" s="6">
-        <v>0</v>
-      </c>
-      <c r="D196" s="6">
-        <v>0</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C196" s="6"/>
+      <c r="D196" s="6"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3">
-        <v>41501</v>
+        <v>20104</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C197" s="6">
-        <v>0</v>
-      </c>
-      <c r="D197" s="6">
-        <v>0</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="C197" s="6"/>
+      <c r="D197" s="6"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="3">
-        <v>41502</v>
+        <v>20105</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C198" s="6">
-        <v>0</v>
-      </c>
-      <c r="D198" s="6">
-        <v>0</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C198" s="6"/>
+      <c r="D198" s="6"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="3">
-        <v>41503</v>
+        <v>20201</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C199" s="6">
-        <v>0</v>
-      </c>
-      <c r="D199" s="6">
-        <v>0</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="C199" s="6"/>
+      <c r="D199" s="6"/>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="3">
-        <v>41601</v>
+        <v>20202</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C200" s="6">
-        <v>0</v>
-      </c>
-      <c r="D200" s="6">
-        <v>0</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="C200" s="6"/>
+      <c r="D200" s="6"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="3">
-        <v>50101</v>
+        <v>20203</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C201" s="6">
-        <v>0</v>
-      </c>
-      <c r="D201" s="6">
-        <v>0</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="C201" s="7"/>
+      <c r="D201" s="7"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3">
-        <v>50102</v>
+        <v>20204</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C202" s="6">
-        <v>0</v>
-      </c>
-      <c r="D202" s="6">
-        <v>5.2791365675719298E-3</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="C202" s="6"/>
+      <c r="D202" s="6"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="3">
-        <v>50103</v>
+        <v>20205</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C203" s="6">
-        <v>0</v>
-      </c>
-      <c r="D203" s="6">
-        <v>0</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C203" s="6"/>
+      <c r="D203" s="6"/>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="3">
-        <v>50104</v>
+        <v>20206</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C204" s="6">
-        <v>0</v>
-      </c>
-      <c r="D204" s="6">
-        <v>0</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C204" s="7"/>
+      <c r="D204" s="7"/>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="3">
-        <v>50201</v>
+        <v>20301</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C205" s="6">
-        <v>0</v>
-      </c>
-      <c r="D205" s="6">
-        <v>0</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C205" s="6"/>
+      <c r="D205" s="6"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="3">
-        <v>50202</v>
+        <v>20302</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C206" s="6">
-        <v>0</v>
-      </c>
-      <c r="D206" s="6">
-        <v>0</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C206" s="6"/>
+      <c r="D206" s="6"/>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="3">
-        <v>50203</v>
+        <v>20303</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C207" s="6">
-        <v>0</v>
-      </c>
-      <c r="D207" s="6">
-        <v>0</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C207" s="6"/>
+      <c r="D207" s="6"/>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="3">
-        <v>50204</v>
+        <v>20304</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C208" s="6">
-        <v>0</v>
-      </c>
-      <c r="D208" s="6">
-        <v>0</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C208" s="6"/>
+      <c r="D208" s="6"/>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="3">
-        <v>50301</v>
+        <v>20305</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C209" s="6">
-        <v>0</v>
-      </c>
-      <c r="D209" s="6">
-        <v>3.2162160898791458E-3</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="C209" s="6"/>
+      <c r="D209" s="6"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3">
-        <v>50302</v>
+        <v>20306</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C210" s="6">
-        <v>0</v>
-      </c>
-      <c r="D210" s="6">
-        <v>0</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C210" s="6"/>
+      <c r="D210" s="6"/>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="3">
-        <v>50303</v>
+        <v>20307</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C211" s="6">
-        <v>0</v>
-      </c>
-      <c r="D211" s="6">
-        <v>0</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C211" s="6"/>
+      <c r="D211" s="6"/>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="3">
-        <v>50401</v>
+        <v>20308</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C212" s="6">
-        <v>0</v>
-      </c>
-      <c r="D212" s="6">
-        <v>0</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C212" s="6"/>
+      <c r="D212" s="6"/>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="3">
-        <v>50402</v>
+        <v>20401</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C213" s="6">
-        <v>0</v>
-      </c>
-      <c r="D213" s="6">
-        <v>0</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="C213" s="6"/>
+      <c r="D213" s="6"/>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="3">
-        <v>50403</v>
+        <v>20403</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C214" s="6">
-        <v>0</v>
-      </c>
-      <c r="D214" s="6">
-        <v>0</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="C214" s="6"/>
+      <c r="D214" s="6"/>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="3">
-        <v>50404</v>
+        <v>20404</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C215" s="6">
-        <v>0</v>
-      </c>
-      <c r="D215" s="6">
-        <v>9.5576207376132406E-3</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="C215" s="6"/>
+      <c r="D215" s="6"/>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="3">
-        <v>50405</v>
+        <v>20405</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C216" s="7">
-        <v>0</v>
-      </c>
-      <c r="D216" s="7">
-        <v>0</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C216" s="6"/>
+      <c r="D216" s="6"/>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="3">
-        <v>50501</v>
+        <v>20604</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C217" s="6">
-        <v>0</v>
-      </c>
-      <c r="D217" s="6">
-        <v>0</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C217" s="6"/>
+      <c r="D217" s="6"/>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="3">
-        <v>50502</v>
+        <v>20605</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C218" s="6">
-        <v>5.7476052483600073E-3</v>
-      </c>
-      <c r="D218" s="6">
-        <v>0</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C218" s="6"/>
+      <c r="D218" s="6"/>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="3">
-        <v>50601</v>
+        <v>20801</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C219" s="6">
-        <v>0</v>
-      </c>
-      <c r="D219" s="6">
-        <v>1.3638592591374907E-2</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C219" s="6"/>
+      <c r="D219" s="6"/>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="3">
-        <v>50602</v>
+        <v>20802</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C220" s="6">
-        <v>0</v>
-      </c>
-      <c r="D220" s="6">
-        <v>1.4409757427212061E-2</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C220" s="6"/>
+      <c r="D220" s="6"/>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="3">
-        <v>50701</v>
+        <v>20803</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C221" s="6">
-        <v>0</v>
-      </c>
-      <c r="D221" s="6">
-        <v>0</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C221" s="6"/>
+      <c r="D221" s="6"/>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="3">
-        <v>50702</v>
+        <v>20804</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C222" s="7">
-        <v>0</v>
-      </c>
-      <c r="D222" s="7">
-        <v>0</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C222" s="6"/>
+      <c r="D222" s="6"/>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="3">
-        <v>50801</v>
+        <v>20805</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C223" s="6">
-        <v>0</v>
-      </c>
-      <c r="D223" s="6">
-        <v>2.1708679844100365E-3</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C223" s="6"/>
+      <c r="D223" s="6"/>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="3">
-        <v>50802</v>
+        <v>20806</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C224" s="6">
-        <v>0</v>
-      </c>
-      <c r="D224" s="6">
-        <v>0</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C224" s="6"/>
+      <c r="D224" s="6"/>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="3">
-        <v>50901</v>
+        <v>20807</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C225" s="6">
-        <v>0</v>
-      </c>
-      <c r="D225" s="6">
-        <v>0</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C225" s="6"/>
+      <c r="D225" s="6"/>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="3">
-        <v>50902</v>
+        <v>20901</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C226" s="6">
-        <v>0</v>
-      </c>
-      <c r="D226" s="6">
-        <v>0</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C226" s="6"/>
+      <c r="D226" s="6"/>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="3">
-        <v>51001</v>
+        <v>20902</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C227" s="6">
-        <v>0</v>
-      </c>
-      <c r="D227" s="6">
-        <v>0</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C227" s="6"/>
+      <c r="D227" s="6"/>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="3">
-        <v>51002</v>
+        <v>20903</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C228" s="6">
-        <v>0</v>
-      </c>
-      <c r="D228" s="6">
-        <v>0</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="C228" s="6"/>
+      <c r="D228" s="6"/>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="3">
-        <v>51003</v>
+        <v>20904</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C229" s="6">
-        <v>0</v>
-      </c>
-      <c r="D229" s="6">
-        <v>0</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="C229" s="6"/>
+      <c r="D229" s="6"/>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="3">
-        <v>51101</v>
+        <v>21004</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C230" s="6">
-        <v>0</v>
-      </c>
-      <c r="D230" s="6">
-        <v>0</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C230" s="6"/>
+      <c r="D230" s="6"/>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="3">
-        <v>51102</v>
+        <v>21201</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C231" s="6">
-        <v>0</v>
-      </c>
-      <c r="D231" s="6">
-        <v>0</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="C231" s="6"/>
+      <c r="D231" s="6"/>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="3">
-        <v>51103</v>
+        <v>21202</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C232" s="6">
-        <v>0</v>
-      </c>
-      <c r="D232" s="6">
-        <v>0</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C232" s="6"/>
+      <c r="D232" s="6"/>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="3">
-        <v>51201</v>
+        <v>21203</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="C233" s="6">
-        <v>0</v>
-      </c>
-      <c r="D233" s="6">
-        <v>0</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C233" s="6"/>
+      <c r="D233" s="6"/>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="3">
-        <v>51202</v>
+        <v>21204</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C234" s="6">
-        <v>0</v>
-      </c>
-      <c r="D234" s="6">
-        <v>0</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="C234" s="6"/>
+      <c r="D234" s="6"/>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="3">
-        <v>51203</v>
+        <v>21301</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C235" s="6">
-        <v>0</v>
-      </c>
-      <c r="D235" s="6">
-        <v>0</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C235" s="6"/>
+      <c r="D235" s="6"/>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="3">
-        <v>51204</v>
+        <v>21302</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C236" s="9">
-        <v>0</v>
-      </c>
-      <c r="D236" s="9">
-        <v>6.190912859701153E-3</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C236" s="6"/>
+      <c r="D236" s="6"/>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="3">
-        <v>51301</v>
+        <v>21303</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C237" s="7">
-        <v>0</v>
-      </c>
-      <c r="D237" s="7">
-        <v>0</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C237" s="6"/>
+      <c r="D237" s="6"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="3">
-        <v>51302</v>
+        <v>21304</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C238" s="6">
-        <v>0</v>
-      </c>
-      <c r="D238" s="6">
-        <v>0</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="C238" s="6"/>
+      <c r="D238" s="6"/>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="3">
-        <v>51401</v>
+        <v>21305</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C239" s="6">
-        <v>0</v>
-      </c>
-      <c r="D239" s="6">
-        <v>0</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C239" s="6"/>
+      <c r="D239" s="6"/>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="3">
-        <v>51402</v>
+        <v>21306</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C240" s="6">
-        <v>0</v>
-      </c>
-      <c r="D240" s="6">
-        <v>0</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C240" s="6"/>
+      <c r="D240" s="6"/>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="3">
-        <v>51501</v>
+        <v>21307</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C241" s="6">
-        <v>0</v>
-      </c>
-      <c r="D241" s="6">
-        <v>4.9006286552371386E-3</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C241" s="6"/>
+      <c r="D241" s="6"/>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="3">
-        <v>51601</v>
+        <v>21701</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C242" s="6">
-        <v>0</v>
-      </c>
-      <c r="D242" s="6">
-        <v>0</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C242" s="6"/>
+      <c r="D242" s="6"/>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="3">
-        <v>60101</v>
+        <v>21702</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C243" s="6">
-        <v>1.0801450915877937E-2</v>
-      </c>
-      <c r="D243" s="6">
-        <v>0.29981005609977096</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C243" s="6"/>
+      <c r="D243" s="6"/>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="3">
-        <v>60201</v>
+        <v>21703</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C244" s="6">
-        <v>7.819745795317104E-2</v>
-      </c>
-      <c r="D244" s="6">
-        <v>0.23473528694888682</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C244" s="6"/>
+      <c r="D244" s="6"/>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="3">
-        <v>60202</v>
+        <v>21801</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C245" s="6">
-        <v>0.29316310885077762</v>
-      </c>
-      <c r="D245" s="6">
-        <v>0.97303880498730266</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C245" s="6"/>
+      <c r="D245" s="6"/>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="3">
-        <v>60301</v>
+        <v>21802</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C246" s="6">
-        <v>1.2901309453422689</v>
-      </c>
-      <c r="D246" s="6">
-        <v>1.1802105164082988</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C246" s="6"/>
+      <c r="D246" s="6"/>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="3">
-        <v>60302</v>
+        <v>21803</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C247" s="6">
-        <v>0.2704646046512198</v>
-      </c>
-      <c r="D247" s="6">
-        <v>0.48739707025536005</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="C247" s="6"/>
+      <c r="D247" s="6"/>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="3">
-        <v>60303</v>
+        <v>21901</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C248" s="6">
-        <v>0.19150728254455138</v>
-      </c>
-      <c r="D248" s="6">
-        <v>0.44244189695765168</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="C248" s="6"/>
+      <c r="D248" s="6"/>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="3">
-        <v>60401</v>
+        <v>21902</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C249" s="6">
-        <v>0</v>
-      </c>
-      <c r="D249" s="6">
-        <v>0.40945696635553408</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="C249" s="6"/>
+      <c r="D249" s="6"/>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="3">
-        <v>60402</v>
+        <v>30401</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C250" s="6">
-        <v>0</v>
-      </c>
-      <c r="D250" s="6">
-        <v>4.0385129848773483E-3</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C250" s="6"/>
+      <c r="D250" s="6"/>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="3">
-        <v>60501</v>
+        <v>30403</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C251" s="6">
-        <v>7.3392323984933722E-3</v>
-      </c>
-      <c r="D251" s="6">
-        <v>0.20089606211517666</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C251" s="6"/>
+      <c r="D251" s="6"/>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="3">
-        <v>60502</v>
+        <v>30404</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C252" s="6">
-        <v>0</v>
-      </c>
-      <c r="D252" s="6">
-        <v>0</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="C252" s="6"/>
+      <c r="D252" s="6"/>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="3">
-        <v>60601</v>
+        <v>30501</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C253" s="6">
-        <v>5.5281311465164663E-2</v>
-      </c>
-      <c r="D253" s="6">
-        <v>0.36968119656543796</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="C253" s="6"/>
+      <c r="D253" s="6"/>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="3">
-        <v>70101</v>
+        <v>30502</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C254" s="6">
-        <v>1.6599139792571078</v>
-      </c>
-      <c r="D254" s="6">
-        <v>0.82365093389118582</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="C254" s="6"/>
+      <c r="D254" s="6"/>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="3">
-        <v>70102</v>
+        <v>30601</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C255" s="6">
-        <v>1.1351462384259183</v>
-      </c>
-      <c r="D255" s="6">
-        <v>1.205676030834425</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C255" s="6"/>
+      <c r="D255" s="6"/>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="3">
-        <v>70103</v>
+        <v>30602</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C256" s="6">
-        <v>2.0781885264475592</v>
-      </c>
-      <c r="D256" s="6">
-        <v>0.82782879464268866</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C256" s="6"/>
+      <c r="D256" s="6"/>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="3">
-        <v>70104</v>
+        <v>30701</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C257" s="6">
-        <v>2.2164392705694982</v>
-      </c>
-      <c r="D257" s="6">
-        <v>0.87534761156129914</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C257" s="6"/>
+      <c r="D257" s="6"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="3">
-        <v>70105</v>
+        <v>30703</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C258" s="6">
-        <v>1.5668017515077088</v>
-      </c>
-      <c r="D258" s="6">
-        <v>0.68246890169232532</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="C258" s="6"/>
+      <c r="D258" s="6"/>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="3">
-        <v>70201</v>
+        <v>30801</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C259" s="6">
-        <v>1.0364682810050185</v>
-      </c>
-      <c r="D259" s="6">
-        <v>0.5772936275058056</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C259" s="6"/>
+      <c r="D259" s="6"/>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="3">
-        <v>70202</v>
+        <v>30802</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="C260" s="6">
-        <v>0.6773711273295725</v>
-      </c>
-      <c r="D260" s="6">
-        <v>0.49182012540925574</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C260" s="6"/>
+      <c r="D260" s="6"/>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="3">
-        <v>70301</v>
+        <v>30803</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C261" s="6">
-        <v>0.22171309238431139</v>
-      </c>
-      <c r="D261" s="6">
-        <v>0.71810049543625021</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C261" s="6"/>
+      <c r="D261" s="6"/>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="3">
-        <v>70302</v>
+        <v>30905</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="C262" s="6">
-        <v>0.15818733731332379</v>
-      </c>
-      <c r="D262" s="6">
-        <v>1.4907538333700081</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C262" s="6"/>
+      <c r="D262" s="6"/>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="3">
-        <v>70303</v>
+        <v>31101</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C263" s="6">
-        <v>0.12404898830205037</v>
-      </c>
-      <c r="D263" s="6">
-        <v>1.1566637893313838</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C263" s="6"/>
+      <c r="D263" s="6"/>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="3">
-        <v>70401</v>
+        <v>31303</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C264" s="6">
-        <v>0.90973365701831221</v>
-      </c>
-      <c r="D264" s="6">
-        <v>0.40420673088101516</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="C264" s="6"/>
+      <c r="D264" s="6"/>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" s="3">
-        <v>70402</v>
+        <v>31401</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C265" s="6">
-        <v>1.4887127163770957</v>
-      </c>
-      <c r="D265" s="6">
-        <v>0.79416795556073416</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C265" s="6"/>
+      <c r="D265" s="6"/>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" s="3">
-        <v>70403</v>
+        <v>31402</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C266" s="6">
-        <v>0.99301048037412809</v>
-      </c>
-      <c r="D266" s="6">
-        <v>0.63892684706017577</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C266" s="6"/>
+      <c r="D266" s="6"/>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" s="3">
-        <v>70404</v>
+        <v>31403</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C267" s="6">
-        <v>1.3000699794434905</v>
-      </c>
-      <c r="D267" s="6">
-        <v>1.5693251307299438</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C267" s="6"/>
+      <c r="D267" s="6"/>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" s="3">
-        <v>70501</v>
+        <v>31404</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C268" s="6">
-        <v>0.2329082844718246</v>
-      </c>
-      <c r="D268" s="6">
-        <v>1.4269415322509753</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C268" s="6"/>
+      <c r="D268" s="6"/>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" s="3">
-        <v>70502</v>
+        <v>31405</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C269" s="6">
-        <v>1.8331428765239755</v>
-      </c>
-      <c r="D269" s="6">
-        <v>1.08032610676566</v>
-      </c>
+        <v>227</v>
+      </c>
+      <c r="C269" s="6"/>
+      <c r="D269" s="6"/>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" s="3">
-        <v>70503</v>
+        <v>31501</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C270" s="6">
-        <v>9.4160047270034367E-2</v>
-      </c>
-      <c r="D270" s="6">
-        <v>2.025120003427789</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C270" s="6"/>
+      <c r="D270" s="6"/>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" s="3">
-        <v>70601</v>
+        <v>40101</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="C271" s="6">
-        <v>2.2664105284764116</v>
-      </c>
-      <c r="D271" s="6">
-        <v>0.87691862164175327</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="C271" s="6"/>
+      <c r="D271" s="6"/>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" s="3">
-        <v>70602</v>
+        <v>40102</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C272" s="6">
-        <v>1.796691669738379</v>
-      </c>
-      <c r="D272" s="6">
-        <v>1.7082854665859581</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C272" s="6"/>
+      <c r="D272" s="6"/>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" s="3">
-        <v>70603</v>
+        <v>40103</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C273" s="6">
-        <v>0.96128956604420357</v>
-      </c>
-      <c r="D273" s="6">
-        <v>1.436853633353145</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C273" s="6"/>
+      <c r="D273" s="6"/>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" s="3">
-        <v>70701</v>
+        <v>40104</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C274" s="6">
-        <v>0.69799514739688251</v>
-      </c>
-      <c r="D274" s="6">
-        <v>0.18618281156905758</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="C274" s="6"/>
+      <c r="D274" s="6"/>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" s="3">
-        <v>70702</v>
+        <v>40201</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C275" s="6">
-        <v>0.31816361001233129</v>
-      </c>
-      <c r="D275" s="6">
-        <v>0.48739222076188882</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="C275" s="6"/>
+      <c r="D275" s="6"/>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="3">
-        <v>70703</v>
+        <v>40202</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C276" s="6">
-        <v>1.279794675919192</v>
-      </c>
-      <c r="D276" s="6">
-        <v>1.0232522378634807</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C276" s="6"/>
+      <c r="D276" s="6"/>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="3">
-        <v>70704</v>
+        <v>40301</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C277" s="6">
-        <v>0.11072481689409375</v>
-      </c>
-      <c r="D277" s="6">
-        <v>1.0557410071933421E-2</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="C277" s="6"/>
+      <c r="D277" s="6"/>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="3">
-        <v>70705</v>
+        <v>40302</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C278" s="6">
-        <v>1.1233568250840498</v>
-      </c>
-      <c r="D278" s="6">
-        <v>0.37316210800105076</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C278" s="6"/>
+      <c r="D278" s="6"/>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
-        <v>70706</v>
+        <v>40401</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C279" s="6">
-        <v>0.4150614455170637</v>
-      </c>
-      <c r="D279" s="6">
-        <v>0.38013493459319331</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="C279" s="6"/>
+      <c r="D279" s="6"/>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
-        <v>70707</v>
+        <v>40402</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C280" s="6">
-        <v>9.6800082597472848E-3</v>
-      </c>
-      <c r="D280" s="6">
-        <v>0.31708187570681451</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="C280" s="6"/>
+      <c r="D280" s="6"/>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
-        <v>70801</v>
+        <v>40501</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C281" s="6">
-        <v>0.1793323671593389</v>
-      </c>
-      <c r="D281" s="6">
-        <v>0.40047724652567285</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="C281" s="6"/>
+      <c r="D281" s="6"/>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
-        <v>70802</v>
+        <v>40502</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C282" s="6">
-        <v>0.15941492169850319</v>
-      </c>
-      <c r="D282" s="6">
-        <v>0.11726882968894096</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="C282" s="6"/>
+      <c r="D282" s="6"/>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
-        <v>70803</v>
+        <v>40503</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C283" s="6">
-        <v>3.1912411417968516E-2</v>
-      </c>
-      <c r="D283" s="6">
-        <v>0.11776422078833867</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="C283" s="6"/>
+      <c r="D283" s="6"/>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
-        <v>70804</v>
+        <v>40504</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C284" s="6">
-        <v>0.20903350570629595</v>
-      </c>
-      <c r="D284" s="6">
-        <v>0.56894051027375003</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="C284" s="6"/>
+      <c r="D284" s="6"/>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
-        <v>70805</v>
+        <v>40505</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="C285" s="6">
-        <v>0.11420307303802221</v>
-      </c>
-      <c r="D285" s="6">
-        <v>0.3128911844334506</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="C285" s="6"/>
+      <c r="D285" s="6"/>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
-        <v>70901</v>
+        <v>40601</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C286" s="7">
-        <v>8.3649446803819472E-2</v>
-      </c>
-      <c r="D286" s="7">
-        <v>0.17464207469019427</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C286" s="6"/>
+      <c r="D286" s="6"/>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
-        <v>70902</v>
+        <v>40602</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C287" s="6">
-        <v>0.38165661813859109</v>
-      </c>
-      <c r="D287" s="6">
-        <v>0.53153545596391372</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="C287" s="6"/>
+      <c r="D287" s="6"/>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
-        <v>70903</v>
+        <v>40603</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="C288" s="6">
-        <v>0.26272761589224441</v>
-      </c>
-      <c r="D288" s="6">
-        <v>0.47805610949675609</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C288" s="6"/>
+      <c r="D288" s="6"/>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
-        <v>70904</v>
+        <v>40701</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C289" s="6">
-        <v>0.27802484702985353</v>
-      </c>
-      <c r="D289" s="6">
-        <v>0.25291672115702429</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C289" s="6"/>
+      <c r="D289" s="6"/>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
-        <v>71001</v>
+        <v>40702</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C290" s="6">
-        <v>0.839299147827123</v>
-      </c>
-      <c r="D290" s="6">
-        <v>0.84922352489470776</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="C290" s="6"/>
+      <c r="D290" s="6"/>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
-        <v>71002</v>
+        <v>40801</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C291" s="6">
-        <v>1.0019892716499768</v>
-      </c>
-      <c r="D291" s="6">
-        <v>0.54465246490061781</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="C291" s="6"/>
+      <c r="D291" s="6"/>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
-        <v>71003</v>
+        <v>40802</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="C292" s="6">
-        <v>1.0114631065388455</v>
-      </c>
-      <c r="D292" s="6">
-        <v>0.96431486429779012</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="C292" s="6"/>
+      <c r="D292" s="6"/>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
-        <v>71004</v>
+        <v>40901</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C293" s="6">
-        <v>0.4805018937720989</v>
-      </c>
-      <c r="D293" s="6">
-        <v>0.21432220244416472</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C293" s="6"/>
+      <c r="D293" s="6"/>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
-        <v>71005</v>
+        <v>40902</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C294" s="6">
-        <v>0.83732866444377829</v>
-      </c>
-      <c r="D294" s="6">
-        <v>0.40496914918942989</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="C294" s="6"/>
+      <c r="D294" s="6"/>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
-        <v>71101</v>
+        <v>40903</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C295" s="6">
-        <v>0.15821153184389056</v>
-      </c>
-      <c r="D295" s="6">
-        <v>0.8371662270510456</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="C295" s="6"/>
+      <c r="D295" s="6"/>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
-        <v>71102</v>
+        <v>41001</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C296" s="6">
-        <v>0.98870419833237566</v>
-      </c>
-      <c r="D296" s="6">
-        <v>1.1873559747518225</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="C296" s="6"/>
+      <c r="D296" s="6"/>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
-        <v>71103</v>
+        <v>41101</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C297" s="6">
-        <v>0.72011588778878011</v>
-      </c>
-      <c r="D297" s="6">
-        <v>1.1671566397954432</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="C297" s="6"/>
+      <c r="D297" s="6"/>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
-        <v>71104</v>
+        <v>41201</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C298" s="6">
-        <v>4.3210677073578463</v>
-      </c>
-      <c r="D298" s="6">
-        <v>0.64172671834567141</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="C298" s="6"/>
+      <c r="D298" s="6"/>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
-        <v>71105</v>
+        <v>41202</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C299" s="6">
-        <v>5.7659280123938887E-2</v>
-      </c>
-      <c r="D299" s="6">
-        <v>0.45725168761237522</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C299" s="6"/>
+      <c r="D299" s="6"/>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
-        <v>71106</v>
+        <v>41301</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C300" s="6">
-        <v>1.3901264518908389</v>
-      </c>
-      <c r="D300" s="6">
-        <v>0.6055652299402593</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="C300" s="6"/>
+      <c r="D300" s="6"/>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
-        <v>71201</v>
+        <v>41401</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C301" s="6">
-        <v>2.6935793844800854E-2</v>
-      </c>
-      <c r="D301" s="6">
-        <v>0.21782823130578241</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C301" s="6"/>
+      <c r="D301" s="6"/>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
-        <v>71301</v>
+        <v>41501</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C302" s="6">
-        <v>0.10600783251507911</v>
-      </c>
-      <c r="D302" s="6">
-        <v>0.11562560573732132</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="C302" s="6"/>
+      <c r="D302" s="6"/>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
-        <v>71302</v>
+        <v>41502</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C303" s="6">
-        <v>2.752828165370827E-2</v>
-      </c>
-      <c r="D303" s="6">
-        <v>0.15775590100214765</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C303" s="6"/>
+      <c r="D303" s="6"/>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
-        <v>71401</v>
+        <v>41503</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C304" s="6">
-        <v>0.13571728172619379</v>
-      </c>
-      <c r="D304" s="6">
-        <v>0.22705037749274634</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C304" s="6"/>
+      <c r="D304" s="6"/>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
-        <v>71402</v>
+        <v>41601</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C305" s="6">
-        <v>0.12701998898704076</v>
-      </c>
-      <c r="D305" s="6">
-        <v>0.15480613333219917</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="C305" s="6"/>
+      <c r="D305" s="6"/>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
-        <v>71403</v>
+        <v>50101</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C306" s="6">
-        <v>0.34432036005587402</v>
-      </c>
-      <c r="D306" s="6">
-        <v>1.1166037097216142</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="C306" s="6"/>
+      <c r="D306" s="6"/>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
-        <v>71501</v>
+        <v>50102</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C307" s="6">
-        <v>0.67137201734431162</v>
-      </c>
-      <c r="D307" s="6">
-        <v>1.8503186071940834</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C307" s="6"/>
+      <c r="D307" s="6"/>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
-        <v>71502</v>
+        <v>50103</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C308" s="6">
-        <v>9.5732985532659236E-3</v>
-      </c>
-      <c r="D308" s="6">
-        <v>0.18603598193553481</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="C308" s="6"/>
+      <c r="D308" s="6"/>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
-        <v>71503</v>
+        <v>50104</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C309" s="6">
-        <v>1.8933227627282803</v>
-      </c>
-      <c r="D309" s="6">
-        <v>1.991867949966813</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C309" s="6"/>
+      <c r="D309" s="6"/>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
-        <v>80101</v>
+        <v>50201</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C310" s="6">
-        <v>4.8410211703786739E-2</v>
-      </c>
-      <c r="D310" s="6">
-        <v>0.1136897208467646</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="C310" s="6"/>
+      <c r="D310" s="6"/>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
-        <v>80102</v>
+        <v>50202</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C311" s="6">
-        <v>8.63432040934385E-2</v>
-      </c>
-      <c r="D311" s="6">
-        <v>0.42676030714172852</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="C311" s="6"/>
+      <c r="D311" s="6"/>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
-        <v>80201</v>
+        <v>50203</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C312" s="6">
-        <v>0.27405699353249757</v>
-      </c>
-      <c r="D312" s="6">
-        <v>0.10031484288148462</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="C312" s="6"/>
+      <c r="D312" s="6"/>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
-        <v>80202</v>
+        <v>50204</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C313" s="6">
-        <v>0.74901975644436691</v>
-      </c>
-      <c r="D313" s="6">
-        <v>0.19793781949335393</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C313" s="6"/>
+      <c r="D313" s="6"/>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
-        <v>80301</v>
+        <v>50302</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C314" s="6">
-        <v>6.5460467625967411E-2</v>
-      </c>
-      <c r="D314" s="6">
-        <v>0.15209644523507648</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C314" s="6"/>
+      <c r="D314" s="6"/>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
-        <v>80302</v>
+        <v>50303</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C315" s="6">
-        <v>0.27451855753058152</v>
-      </c>
-      <c r="D315" s="6">
-        <v>0.31751526008971076</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C315" s="6"/>
+      <c r="D315" s="6"/>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
-        <v>80303</v>
+        <v>50403</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C316" s="6">
-        <v>1.4570782745680983E-2</v>
-      </c>
-      <c r="D316" s="6">
-        <v>8.2752073179950439E-2</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C316" s="6"/>
+      <c r="D316" s="6"/>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
-        <v>80304</v>
+        <v>50404</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C317" s="6">
-        <v>0.3353843734033361</v>
-      </c>
-      <c r="D317" s="6">
-        <v>0.46887023447927562</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C317" s="6"/>
+      <c r="D317" s="6"/>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
-        <v>80401</v>
+        <v>50405</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="C318" s="6">
-        <v>5.6304779707764846E-2</v>
-      </c>
-      <c r="D318" s="6">
-        <v>5.7388225745097617E-2</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="C318" s="7"/>
+      <c r="D318" s="7"/>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
-        <v>80402</v>
+        <v>50601</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C319" s="6">
-        <v>1.1086441351722799E-2</v>
-      </c>
-      <c r="D319" s="6">
-        <v>2.866831763855035E-2</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="C319" s="6"/>
+      <c r="D319" s="6"/>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
-        <v>80501</v>
+        <v>50602</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C320" s="6">
-        <v>1.789118067534488E-2</v>
-      </c>
-      <c r="D320" s="6">
-        <v>6.0933048198979232E-2</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C320" s="6"/>
+      <c r="D320" s="6"/>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
-        <v>80601</v>
+        <v>50701</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C321" s="6">
-        <v>1.5874399110218092E-2</v>
-      </c>
-      <c r="D321" s="6">
-        <v>5.0164238174668578E-2</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C321" s="6"/>
+      <c r="D321" s="6"/>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
-        <v>80602</v>
+        <v>50702</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C322" s="6">
-        <v>0.24319717043159192</v>
-      </c>
-      <c r="D322" s="6">
-        <v>0.93997682372846725</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="C322" s="7"/>
+      <c r="D322" s="7"/>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
-        <v>80701</v>
+        <v>50801</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C323" s="6">
-        <v>3.5308274054465745E-2</v>
-      </c>
-      <c r="D323" s="6">
-        <v>4.2324546221992658E-2</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="C323" s="6"/>
+      <c r="D323" s="6"/>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
-        <v>80702</v>
+        <v>50802</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C324" s="6">
-        <v>2.3948495043991817E-2</v>
-      </c>
-      <c r="D324" s="6">
-        <v>3.2937244678818874E-2</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C324" s="6"/>
+      <c r="D324" s="6"/>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
-        <v>80703</v>
+        <v>50901</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C325" s="6">
-        <v>3.3030824990643956E-2</v>
-      </c>
-      <c r="D325" s="6">
-        <v>0.15730275735975138</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C325" s="6"/>
+      <c r="D325" s="6"/>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
-        <v>80801</v>
+        <v>50902</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C326" s="6">
-        <v>1.5310409880997369E-2</v>
-      </c>
-      <c r="D326" s="6">
-        <v>4.0663623654086378E-2</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="C326" s="6"/>
+      <c r="D326" s="6"/>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
-        <v>80802</v>
+        <v>51001</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C327" s="6">
-        <v>1.7787426793790348E-2</v>
-      </c>
-      <c r="D327" s="6">
-        <v>9.0209310848399893E-2</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="C327" s="6"/>
+      <c r="D327" s="6"/>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
-        <v>80803</v>
+        <v>51002</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C328" s="6">
-        <v>7.6598096465664385E-3</v>
-      </c>
-      <c r="D328" s="6">
-        <v>0.10281896284401074</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="C328" s="6"/>
+      <c r="D328" s="6"/>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
-        <v>80901</v>
+        <v>51003</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C329" s="9">
-        <v>1.6869993655159673E-2</v>
-      </c>
-      <c r="D329" s="9">
-        <v>8.655804011357153E-2</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="C329" s="6"/>
+      <c r="D329" s="6"/>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
-        <v>90101</v>
+        <v>51101</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C330" s="6">
-        <v>0.83323099028835657</v>
-      </c>
-      <c r="D330" s="6">
-        <v>1.1045815777623671</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C330" s="6"/>
+      <c r="D330" s="6"/>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
-        <v>90102</v>
+        <v>51102</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="C331" s="7">
-        <v>0.57291852844216251</v>
-      </c>
-      <c r="D331" s="7">
-        <v>0.70467817718445447</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="C331" s="6"/>
+      <c r="D331" s="6"/>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
-        <v>90103</v>
+        <v>51103</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C332" s="6">
-        <v>0.32970506406161704</v>
-      </c>
-      <c r="D332" s="6">
-        <v>0.47877964825727243</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="C332" s="6"/>
+      <c r="D332" s="6"/>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
-        <v>90104</v>
+        <v>51201</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C333" s="6">
-        <v>0.26824887653210744</v>
-      </c>
-      <c r="D333" s="6">
-        <v>0.43730645606278179</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="C333" s="6"/>
+      <c r="D333" s="6"/>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
-        <v>90201</v>
+        <v>51202</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C334" s="6">
-        <v>0.102116295556402</v>
-      </c>
-      <c r="D334" s="6">
-        <v>6.6665266524600919E-2</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="C334" s="6"/>
+      <c r="D334" s="6"/>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
-        <v>90202</v>
+        <v>51203</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C335" s="6">
-        <v>0.14001641673480761</v>
-      </c>
-      <c r="D335" s="6">
-        <v>7.7111164966284229E-2</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="C335" s="6"/>
+      <c r="D335" s="6"/>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
-        <v>90203</v>
+        <v>51204</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C336" s="6">
-        <v>0.10232434515391299</v>
-      </c>
-      <c r="D336" s="6">
-        <v>0.21185884142306322</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="C336" s="9"/>
+      <c r="D336" s="9"/>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
-        <v>90301</v>
+        <v>51301</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="C337" s="6">
-        <v>0.20292288064260233</v>
-      </c>
-      <c r="D337" s="6">
-        <v>0.30084816334701681</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C337" s="7"/>
+      <c r="D337" s="7"/>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
-        <v>90302</v>
+        <v>51302</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C338" s="6">
-        <v>8.1918509521273802E-2</v>
-      </c>
-      <c r="D338" s="6">
-        <v>0.10120030302316683</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="C338" s="6"/>
+      <c r="D338" s="6"/>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
-        <v>90303</v>
+        <v>51401</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="C339" s="6">
-        <v>2.8246508442810993E-2</v>
-      </c>
-      <c r="D339" s="6">
-        <v>7.0352311661754735E-2</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="C339" s="6"/>
+      <c r="D339" s="6"/>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
-        <v>90401</v>
+        <v>51402</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C340" s="6">
-        <v>0.10187843767805958</v>
-      </c>
-      <c r="D340" s="6">
-        <v>8.974889414762971E-2</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C340" s="6"/>
+      <c r="D340" s="6"/>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
-        <v>90402</v>
+        <v>51501</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C341" s="6">
-        <v>2.612832326779501E-2</v>
-      </c>
-      <c r="D341" s="6">
-        <v>3.162543131870111E-2</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="C341" s="6"/>
+      <c r="D341" s="6"/>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
-        <v>90501</v>
+        <v>51601</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C342" s="6">
-        <v>4.0971303293324469E-2</v>
-      </c>
-      <c r="D342" s="6">
-        <v>2.3233547266592155E-2</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="C342" s="6"/>
+      <c r="D342" s="6"/>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
-        <v>90502</v>
+        <v>60402</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C343" s="6">
-        <v>3.276832061013981E-2</v>
-      </c>
-      <c r="D343" s="6">
-        <v>1.901734560941222E-2</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="C343" s="6"/>
+      <c r="D343" s="6"/>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
-        <v>90503</v>
+        <v>60502</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C344" s="6">
-        <v>1.3689271521057027E-2</v>
-      </c>
-      <c r="D344" s="6">
-        <v>1.3734351413043853E-2</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="C344" s="6"/>
+      <c r="D344" s="6"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D351">
@@ -25587,6 +25203,9 @@
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
